--- a/output/StructureDefinition-BRMedicamento.xlsx
+++ b/output/StructureDefinition-BRMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T19:02:54-03:00</t>
+    <t>2026-09-22T22:11:28-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedicamento.xlsx
+++ b/output/StructureDefinition-BRMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T22:11:28-03:00</t>
+    <t>2026-09-30T19:01:17-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedicamento.xlsx
+++ b/output/StructureDefinition-BRMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:01:17-03:00</t>
+    <t>2026-10-08T21:31:18-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
